--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>27/07 13:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>26/07 12:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="F3" t="n">
+        <v>3.25</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>26/07 22:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>26/07 21:30</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>55</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>26/07 22:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>55</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>28/07 23:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>60</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>30/07 17:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>60</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>02/08 18:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>50</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>26/07 15:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>45</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>26/07 18:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>45</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>30/07 18:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>55</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>27/07 19:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>55</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>50</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>03/08 00:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>50</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>27/07 01:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>45</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>30/07 17:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>60</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>26/07 18:30</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>40</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>26/07 15:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>40</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>27/07 11:35</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>50</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>26/07 15:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>40</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>03/08 22:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>45</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>26/07 23:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>45</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>26/07 21:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F24" t="n">
+        <v>2.85</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>27/07 18:30</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>40</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>02/08 18:30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>35</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,187 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45864.07902157337</v>
+        <v>45864.07902157407</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Guadalajar</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Guadalajara – Atletico San LuisLiga MX</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>26/07 23:05</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+6,78%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45864.15053319324</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 8.5 - tir cadré | Inter Miam</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Inter Miami CF – FC CincinnatiÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>26/07 23:15</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>36,5%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+5,77%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45864.15053319324</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 5.5 - tir cadré2e équipe | Sport Reci</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sport Recife – SantosBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>26/07 21:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>22,7%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+2,04%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45864.15053319324</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Pas de buts | Paksi – WK</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Paksi – WKW ETO FC GyorOTP Bank Liga</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>27/07 16:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+1,38%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45864.15053319324</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>26/07 23:05</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>45</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45864.15053319324</v>
+        <v>45864.15053319444</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>26/07 23:15</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F28" t="n">
+        <v>2.9</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45864.15053319324</v>
+        <v>45864.15053319444</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>26/07 21:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="F29" t="n">
+        <v>4.5</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45864.15053319324</v>
+        <v>45864.15053319444</v>
       </c>
     </row>
     <row r="30">
@@ -1715,10 +1709,8 @@
           <t>27/07 16:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>18.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>18</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1731,7 +1723,97 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45864.15053319324</v>
+        <v>45864.15053319444</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Racing Clu</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Racing Club – Estudiantes de La PlataLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>27/07 00:15</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2,50%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+12,7%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45864.19349021162</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Monterrey </t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Monterrey – Atlas FCLiga MX</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>27/07 01:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+6,16%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45864.19349021162</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>27/07 00:15</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>45</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45864.19349021162</v>
+        <v>45864.19349020833</v>
       </c>
     </row>
     <row r="32">
@@ -1797,23 +1795,111 @@
           <t>27/07 01:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="n">
+        <v>45</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+6,16%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45864.19349020833</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | SV Ried – </t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SV Ried – RB SalzbourgBundesliga</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>02/08 17:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>+6,16%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>45864.19349021162</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+7,53%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45864.22571859966</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 8.5 - tir cadré | Real Salt </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Real Salt Lake – San Jose EarthquakesÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>27/07 01:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>33,6%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+4,08%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45864.22571859966</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,10 +1838,8 @@
           <t>02/08 17:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>45</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45864.22571859966</v>
+        <v>45864.22571859954</v>
       </c>
     </row>
     <row r="34">
@@ -1883,10 +1881,8 @@
           <t>27/07 01:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F34" t="n">
+        <v>3.1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1899,7 +1895,232 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45864.22571859966</v>
+        <v>45864.22571859954</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Botafogo –</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Botafogo – CorinthiansSérie A</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>26/07 21:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>17,5%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+232%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45864.27312454284</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 9.5 - tir cadré | Internacio</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Internacional RS – Vasco de GamaBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>27/07 21:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>43,9%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+16,2%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45864.27312454284</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Tennis | 1 - aces | Alexander </t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Alexander Bublik – Arthur CazauxATP - Kitzbühel</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>26/07 12:30</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>84,6%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+14,2%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45864.27312454284</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 10.5 - tir cadré | Flamengo –</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Flamengo – Atletico Mineiro385076e7 Brésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>27/07 23:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>29,1%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+13,6%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45864.27312454284</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 9.5 - tir cadré | Cruzeiro –</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Cruzeiro – Ceara CEBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>27/07 19:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>35,9%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+7,82%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45864.27312454284</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1924,10 +1924,8 @@
           <t>26/07 21:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>19</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1940,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45864.27312454284</v>
+        <v>45864.27312454861</v>
       </c>
     </row>
     <row r="36">
@@ -1969,10 +1967,8 @@
           <t>27/07 21:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
+      <c r="F36" t="n">
+        <v>2.65</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1985,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45864.27312454284</v>
+        <v>45864.27312454861</v>
       </c>
     </row>
     <row r="37">
@@ -2014,10 +2010,8 @@
           <t>26/07 12:30</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
+      <c r="F37" t="n">
+        <v>1.35</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2030,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45864.27312454284</v>
+        <v>45864.27312454861</v>
       </c>
     </row>
     <row r="38">
@@ -2059,10 +2053,8 @@
           <t>27/07 23:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="F38" t="n">
+        <v>3.9</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2075,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45864.27312454284</v>
+        <v>45864.27312454861</v>
       </c>
     </row>
     <row r="39">
@@ -2104,10 +2096,8 @@
           <t>27/07 19:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>3</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2120,7 +2110,52 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45864.27312454284</v>
+        <v>45864.27312454861</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 4.5 - tir cadré1re équipe | Sao Paulo </t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sao Paulo SP – FluminenseBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>27/07 19:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>42,9%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+5,03%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45864.30719468</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -2139,10 +2139,8 @@
           <t>27/07 19:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="F40" t="n">
+        <v>2.45</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45864.30719468</v>
+        <v>45864.30719467592</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2156,6 +2156,96 @@
         <v>45864.30719467592</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 8.5 - tir cadré | Philadelph</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Philadelphia Union – Colorado RapidsÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>26/07 23:30</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>38,2%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+4,98%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45864.39106665416</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Radnicki K</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Radnicki Kragujevac – Zeleznicar PancevoSuperLiga</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>27/07 18:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+2,66%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45864.39106665416</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,10 +2182,8 @@
           <t>26/07 23:30</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F41" t="n">
+        <v>2.75</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45864.39106665416</v>
+        <v>45864.39106665509</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>27/07 18:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>40</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,97 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45864.39106665416</v>
+        <v>45864.39106665509</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 18.5 - tirs1re équipe | Cruzeiro –</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Cruzeiro – Ceara CEBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 18.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>27/07 19:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>35,8%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+11,0%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45864.43309186494</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 16.5 - tirs1re équipe | Pogon Szcz</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Pogon Szczecin – Motor LublinPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 16.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>26/07 15:30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>50,3%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+10,7%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45864.43309186494</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2268,10 +2268,8 @@
           <t>27/07 19:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F43" t="n">
+        <v>3.1</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2284,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45864.43309186494</v>
+        <v>45864.43309186342</v>
       </c>
     </row>
     <row r="44">
@@ -2313,10 +2311,8 @@
           <t>26/07 15:30</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F44" t="n">
+        <v>2.2</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2329,7 +2325,142 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45864.43309186494</v>
+        <v>45864.43309186342</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 27.5 - tirs | Atlanta Un</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Atlanta United – Seattle SoundersÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 27.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>26/07 23:30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>45,1%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+30,7%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45864.47199174148</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 9.5 - tir cadré | Zulte Ware</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Zulte Waregem – MalinesBelgique - Belgique Division 1A</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>26/07 16:15</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>51,3%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+11,8%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45864.47199174148</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Legia Vars</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Legia Varsovie – FC Banik OstravaLigue Europa</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>31/07 19:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45864.47199174148</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2354,10 +2354,8 @@
           <t>26/07 23:30</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F45" t="n">
+        <v>2.9</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2370,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45864.47199174148</v>
+        <v>45864.47199173611</v>
       </c>
     </row>
     <row r="46">
@@ -2399,10 +2397,8 @@
           <t>26/07 16:15</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2.18</t>
-        </is>
+      <c r="F46" t="n">
+        <v>2.18</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2415,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45864.47199174148</v>
+        <v>45864.47199173611</v>
       </c>
     </row>
     <row r="47">
@@ -2444,23 +2440,201 @@
           <t>31/07 19:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" t="n">
+        <v>40</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45864.47199173611</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 10.5 - tirs2e équipe | Flamengo –</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Flamengo – Atletico MineiroBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>27/07 23:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>38,6%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+15,7%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45864.53028276007</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | Moins que 8.52e set | A.Ruzic – </t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>A.Ruzic – Plekhanova, DashaWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Moins que 8.52e set</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>26/07 16:20</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+15,0%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45864.53028276007</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 30.5 - tirs | Real Salt </t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Real Salt Lake – San Jose EarthquakesÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 30.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>27/07 01:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>43,1%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+14,1%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45864.53028276007</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | AEK Larnac</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AEK Larnaca – NK CeljeLigue Europa</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>31/07 16:30</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>+10,0%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>45864.47199174148</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+8,64%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45864.53028276007</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2483,10 +2483,8 @@
           <t>27/07 23:30</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>3</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2499,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45864.53028276007</v>
+        <v>45864.53028275463</v>
       </c>
     </row>
     <row r="49">
@@ -2528,10 +2526,8 @@
           <t>26/07 16:20</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="F49" t="n">
+        <v>2.3</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2544,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45864.53028276007</v>
+        <v>45864.53028275463</v>
       </c>
     </row>
     <row r="50">
@@ -2573,10 +2569,8 @@
           <t>27/07 01:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
+      <c r="F50" t="n">
+        <v>2.65</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2589,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45864.53028276007</v>
+        <v>45864.53028275463</v>
       </c>
     </row>
     <row r="51">
@@ -2618,10 +2612,8 @@
           <t>31/07 16:30</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>40</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2634,7 +2626,52 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45864.53028276007</v>
+        <v>45864.53028275463</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 10.5 - tirs2e équipe | Pogon Szcz</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Pogon Szczecin – Motor LublinPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Moins que 10.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>26/07 15:30</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>49,4%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+10,2%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45864.56523695473</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -2655,10 +2655,8 @@
           <t>26/07 15:30</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
+      <c r="F52" t="n">
+        <v>2.23</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2671,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45864.56523695473</v>
+        <v>45864.56523695602</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2672,6 +2672,96 @@
         <v>45864.56523695602</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 2(0:1) | AZ Alkmaar</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar – Ilves TampereEurope. Europa Conférence (Q)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2(0:1)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>31/07 16:45</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>5.80</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>17,9%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+3,82%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45864.64097888802</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CA Huracan</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CA Huracan – Boca JuniorsLiga Profesional A9ZJ2X7R 385076e7</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>27/07 21:30</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+3,64%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45864.64097888802</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,10 +2698,8 @@
           <t>31/07 16:45</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>5.80</t>
-        </is>
+      <c r="F53" t="n">
+        <v>5.8</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45864.64097888802</v>
+        <v>45864.64097888889</v>
       </c>
     </row>
     <row r="54">
@@ -2743,10 +2741,8 @@
           <t>27/07 21:30</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>40</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2759,7 +2755,142 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45864.64097888802</v>
+        <v>45864.64097888889</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 4.5 - tir cadré1re équipe | Lechia Gda</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Lechia Gdansk – Lech PoznanPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>26/07 18:15</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>46,6%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+14,2%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45864.68582035126</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 27.5 - tirs | Flamengo –</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Flamengo – Atletico MineiroBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Plus que 27.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>27/07 23:30</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>39,0%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+11,0%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45864.68582035126</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 8.5 - tir cadré | Raal La Lo</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Raal La Louviere – Standard LiègeBelgique - Belgique Division 1A</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plus que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>26/07 18:45</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>51,2%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+1,91%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45864.68582035126</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,10 +2784,8 @@
           <t>26/07 18:15</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="F55" t="n">
+        <v>2.45</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2800,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45864.68582035126</v>
+        <v>45864.68582034722</v>
       </c>
     </row>
     <row r="56">
@@ -2829,10 +2827,8 @@
           <t>27/07 23:30</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F56" t="n">
+        <v>2.85</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2845,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45864.68582035126</v>
+        <v>45864.68582034722</v>
       </c>
     </row>
     <row r="57">
@@ -2874,10 +2870,8 @@
           <t>26/07 18:45</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
+      <c r="F57" t="n">
+        <v>1.99</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2890,7 +2884,187 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45864.68582035126</v>
+        <v>45864.68582034722</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 6.5 - tir cadré1re équipe | Mirassol –</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Mirassol – Vitoria BABrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 6.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>26/07 21:30</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>30,9%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+11,1%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45864.72372172273</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 5.5 - tir cadré1re équipe | Sint-Truid</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Sint-Truidense VV – La GantoiseBelgique - Belgique Division 1A</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>27/07 17:15</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>41,0%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+3,74%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45864.72372172273</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 8.5 - tir cadré | Internacio</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Internacional RS – Vasco de GamaBrésil - Brésil Série A A9ZJ2X7R 385076e7</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>27/07 21:30</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>47,4%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+1,97%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45864.72372172273</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 4.5 - tir cadré1re équipe | Oud-Heverl</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Oud-Heverlee Leuven – Royal Charleroi SCBelgique - Belgique Division 1A</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>27/07 14:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>37,3%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+1,57%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45864.72372172273</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2913,10 +2913,8 @@
           <t>26/07 21:30</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="F58" t="n">
+        <v>3.6</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2929,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45864.72372172273</v>
+        <v>45864.72372172453</v>
       </c>
     </row>
     <row r="59">
@@ -2958,10 +2956,8 @@
           <t>27/07 17:15</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
+      <c r="F59" t="n">
+        <v>2.53</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2974,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45864.72372172273</v>
+        <v>45864.72372172453</v>
       </c>
     </row>
     <row r="60">
@@ -3003,10 +2999,8 @@
           <t>27/07 21:30</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="F60" t="n">
+        <v>2.15</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3019,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45864.72372172273</v>
+        <v>45864.72372172453</v>
       </c>
     </row>
     <row r="61">
@@ -3048,10 +3042,8 @@
           <t>27/07 14:00</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2.72</t>
-        </is>
+      <c r="F61" t="n">
+        <v>2.72</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3064,7 +3056,232 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45864.72372172273</v>
+        <v>45864.72372172453</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | CA Platens</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CA Platense – Argentinos JuniorsLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>26/07 22:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>70.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+31,8%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45864.77191939062</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 3.5 - tir cadré2e équipe | Cruzeiro –</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Cruzeiro – Ceara CEBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>27/07 19:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>32,7%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+1,39%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45864.77191939062</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Deportivo </t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra – Atletico TucumanLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>28/07 19:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+1,14%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45864.77191939062</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Moins que 1.5 - break1er participant | Corentin M</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Corentin Moutet – Alex De MinaurATP - Washington</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Moins que 1.5 - break1er participant</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>26/07 23:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>48,1%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+0,93%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45864.77191939062</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Sao Paulo </t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Sao Paulo – FluminenseSérie A</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>27/07 19:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+0,60%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45864.77191939062</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3085,10 +3085,8 @@
           <t>26/07 22:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>70</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3101,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45864.77191939062</v>
+        <v>45864.77191938657</v>
       </c>
     </row>
     <row r="63">
@@ -3130,10 +3128,8 @@
           <t>27/07 19:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F63" t="n">
+        <v>3.1</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3146,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45864.77191939062</v>
+        <v>45864.77191938657</v>
       </c>
     </row>
     <row r="64">
@@ -3175,10 +3171,8 @@
           <t>28/07 19:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>40</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3191,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45864.77191939062</v>
+        <v>45864.77191938657</v>
       </c>
     </row>
     <row r="65">
@@ -3220,10 +3214,8 @@
           <t>26/07 23:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F65" t="n">
+        <v>2.1</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3236,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45864.77191939062</v>
+        <v>45864.77191938657</v>
       </c>
     </row>
     <row r="66">
@@ -3265,10 +3257,8 @@
           <t>27/07 19:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F66" t="n">
+        <v>45</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3281,7 +3271,52 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45864.77191939062</v>
+        <v>45864.77191938657</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Atletico M</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Atletico Mineiro – Red Bull BragantinoSérie A</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>03/08 21:30</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+1,01%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45864.80423166679</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3300,10 +3300,8 @@
           <t>03/08 21:30</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>40</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3316,7 +3314,142 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45864.80423166679</v>
+        <v>45864.80423166667</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tirs2e équipe | Philadelph</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Philadelphia Union – Colorado RapidsÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>26/07 23:30</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>34,5%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+10,3%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45864.85054396932</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 10.5 - tirs2e équipe | Charlotte </t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Charlotte FC – Toronto FCÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Moins que 10.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>26/07 23:30</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>57,0%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+3,79%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45864.85054396932</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 22.5 - tirs | DC United </t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>DC United – Austin FCÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Moins que 22.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>26/07 23:30</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>36,7%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+2,69%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45864.85054396932</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3343,10 +3343,8 @@
           <t>26/07 23:30</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F68" t="n">
+        <v>3.2</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3359,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45864.85054396932</v>
+        <v>45864.85054396991</v>
       </c>
     </row>
     <row r="69">
@@ -3388,10 +3386,8 @@
           <t>26/07 23:30</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
+      <c r="F69" t="n">
+        <v>1.82</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3404,7 +3400,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45864.85054396932</v>
+        <v>45864.85054396991</v>
       </c>
     </row>
     <row r="70">
@@ -3433,10 +3429,8 @@
           <t>26/07 23:30</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F70" t="n">
+        <v>2.8</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3449,7 +3443,97 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45864.85054396932</v>
+        <v>45864.85054396991</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Club Gener</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Club General Caballero JLM – Sportivo TrinidensePrimera Division</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>29/07 19:00</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+12,6%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45864.8895655555</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 2 | Borac Banj</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Borac Banja Luka – Rudar PrijedorBosnie. Bosnie - Premier League</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>27/07 19:00</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+2,45%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45864.8895655555</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3472,10 +3472,8 @@
           <t>29/07 19:00</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F71" t="n">
+        <v>40</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3488,7 +3486,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45864.8895655555</v>
+        <v>45864.88956555555</v>
       </c>
     </row>
     <row r="72">
@@ -3517,10 +3515,8 @@
           <t>27/07 19:00</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>18.00</t>
-        </is>
+      <c r="F72" t="n">
+        <v>18</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3533,7 +3529,97 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45864.8895655555</v>
+        <v>45864.88956555555</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 9.5 - tirs2e équipe | Philadelph</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Philadelphia Union – Colorado RapidsÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>26/07 23:30</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>55,3%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+4,04%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45864.93206179508</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Basketball | H 2 (−3.5)4e période | Dallas Win</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Dallas Wings – Las Vegas AcesUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>H 2 (−3.5)4e période</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>27/07 20:00</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>46,3%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+3,64%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45864.93206179508</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-26.xlsx
+++ b/data/valuebets_database_2025-07-26.xlsx
@@ -3558,10 +3558,8 @@
           <t>26/07 23:30</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
+      <c r="F73" t="n">
+        <v>1.88</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3574,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45864.93206179508</v>
+        <v>45864.93206179398</v>
       </c>
     </row>
     <row r="74">
@@ -3603,10 +3601,8 @@
           <t>27/07 20:00</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
+      <c r="F74" t="n">
+        <v>2.24</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3619,7 +3615,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45864.93206179508</v>
+        <v>45864.93206179398</v>
       </c>
     </row>
   </sheetData>
